--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run3/epoch_80/per_file_predictions_epoch_80.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run3/epoch_80/per_file_predictions_epoch_80.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="522">
   <si>
     <t>Filename</t>
   </si>
@@ -808,772 +808,778 @@
     <t>0,1,1,0</t>
   </si>
   <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
     <t>0,1,0,1</t>
   </si>
   <si>
-    <t>0.6773,0.0712,0.0548,0.2029</t>
-  </si>
-  <si>
-    <t>0.0030,0.0091,0.0008,0.9975</t>
-  </si>
-  <si>
-    <t>0.8099,0.0159,0.0335,0.1248</t>
-  </si>
-  <si>
-    <t>0.1234,0.0041,0.0008,0.9649</t>
-  </si>
-  <si>
-    <t>0.9922,0.0033,0.0007,0.0008</t>
-  </si>
-  <si>
-    <t>0.9925,0.0021,0.0003,0.0017</t>
-  </si>
-  <si>
-    <t>0.9861,0.0101,0.0010,0.0010</t>
-  </si>
-  <si>
-    <t>0.9909,0.0027,0.0009,0.0021</t>
-  </si>
-  <si>
-    <t>0.9907,0.0059,0.0008,0.0006</t>
-  </si>
-  <si>
-    <t>0.9873,0.0129,0.0008,0.0007</t>
-  </si>
-  <si>
-    <t>0.9903,0.0045,0.0009,0.0014</t>
-  </si>
-  <si>
-    <t>0.9931,0.0013,0.0003,0.0016</t>
-  </si>
-  <si>
-    <t>0.6461,0.0572,0.3495,0.0109</t>
-  </si>
-  <si>
-    <t>0.3679,0.0591,0.6236,0.0326</t>
-  </si>
-  <si>
-    <t>0.2908,0.0237,0.7199,0.0008</t>
-  </si>
-  <si>
-    <t>0.2404,0.0222,0.7549,0.0055</t>
-  </si>
-  <si>
-    <t>0.3429,0.0812,0.6169,0.0251</t>
-  </si>
-  <si>
-    <t>0.0144,0.9803,0.0017,0.0006</t>
-  </si>
-  <si>
-    <t>0.0486,0.9578,0.0047,0.0004</t>
-  </si>
-  <si>
-    <t>0.7399,0.3174,0.0211,0.0024</t>
-  </si>
-  <si>
-    <t>0.0607,0.9490,0.0037,0.0001</t>
-  </si>
-  <si>
-    <t>0.0100,0.9875,0.0014,0.0001</t>
-  </si>
-  <si>
-    <t>0.5641,0.0077,0.4112,0.0287</t>
-  </si>
-  <si>
-    <t>0.3660,0.0231,0.6382,0.0280</t>
-  </si>
-  <si>
-    <t>0.0298,0.0247,0.9517,0.0071</t>
-  </si>
-  <si>
-    <t>0.1173,0.0216,0.8858,0.0103</t>
-  </si>
-  <si>
-    <t>0.0616,0.0209,0.9172,0.0094</t>
-  </si>
-  <si>
-    <t>0.0646,0.0137,0.9178,0.0155</t>
-  </si>
-  <si>
-    <t>0.0114,0.0097,0.9850,0.0016</t>
-  </si>
-  <si>
-    <t>0.6825,0.3063,0.0610,0.0036</t>
-  </si>
-  <si>
-    <t>0.5761,0.1786,0.3241,0.0154</t>
-  </si>
-  <si>
-    <t>0.0003,0.0065,0.9966,0.0031</t>
-  </si>
-  <si>
-    <t>0.0898,0.7485,0.2452,0.0023</t>
-  </si>
-  <si>
-    <t>0.7252,0.1916,0.0652,0.1085</t>
-  </si>
-  <si>
-    <t>0.8363,0.1701,0.0103,0.0162</t>
-  </si>
-  <si>
-    <t>0.8669,0.2017,0.0057,0.0010</t>
-  </si>
-  <si>
-    <t>0.1725,0.8429,0.0668,0.0021</t>
-  </si>
-  <si>
-    <t>0.0309,0.8568,0.2091,0.0343</t>
-  </si>
-  <si>
-    <t>0.0763,0.0431,0.9089,0.0153</t>
-  </si>
-  <si>
-    <t>0.0434,0.1658,0.8783,0.0048</t>
-  </si>
-  <si>
-    <t>0.0820,0.0093,0.7628,0.1270</t>
-  </si>
-  <si>
-    <t>0.0465,0.0367,0.9071,0.0298</t>
-  </si>
-  <si>
-    <t>0.0084,0.9542,0.0839,0.0116</t>
-  </si>
-  <si>
-    <t>0.0375,0.1570,0.8734,0.0370</t>
-  </si>
-  <si>
-    <t>0.0071,0.8338,0.0092,0.9004</t>
-  </si>
-  <si>
-    <t>0.0007,0.9897,0.0139,0.0406</t>
-  </si>
-  <si>
-    <t>0.0015,0.9782,0.4049,0.0007</t>
-  </si>
-  <si>
-    <t>0.0008,0.9893,0.1211,0.0041</t>
-  </si>
-  <si>
-    <t>0.0037,0.2654,0.9749,0.0006</t>
-  </si>
-  <si>
-    <t>0.0023,0.0323,0.9877,0.0042</t>
-  </si>
-  <si>
-    <t>0.0240,0.0385,0.9635,0.0050</t>
-  </si>
-  <si>
-    <t>0.0688,0.0034,0.9527,0.0027</t>
-  </si>
-  <si>
-    <t>0.0074,0.0075,0.9890,0.0013</t>
-  </si>
-  <si>
-    <t>0.0310,0.0194,0.9566,0.0013</t>
-  </si>
-  <si>
-    <t>0.9424,0.0613,0.0018,0.0046</t>
-  </si>
-  <si>
-    <t>0.9195,0.0322,0.0458,0.0094</t>
-  </si>
-  <si>
-    <t>0.9646,0.0138,0.0080,0.0078</t>
-  </si>
-  <si>
-    <t>0.0047,0.1386,0.9785,0.0082</t>
-  </si>
-  <si>
-    <t>0.9677,0.0104,0.0074,0.0092</t>
-  </si>
-  <si>
-    <t>0.9829,0.0101,0.0030,0.0016</t>
-  </si>
-  <si>
-    <t>0.8966,0.1102,0.0226,0.0070</t>
-  </si>
-  <si>
-    <t>0.0059,0.9358,0.4868,0.0012</t>
-  </si>
-  <si>
-    <t>0.0020,0.0215,0.9793,0.0166</t>
-  </si>
-  <si>
-    <t>0.0009,0.0092,0.9824,0.0272</t>
-  </si>
-  <si>
-    <t>0.0005,0.8914,0.9597,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.0066,0.9965,0.0017</t>
-  </si>
-  <si>
-    <t>0.0233,0.9648,0.0130,0.0006</t>
-  </si>
-  <si>
-    <t>0.0092,0.9882,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.8772,0.0460,0.0596,0.0151</t>
-  </si>
-  <si>
-    <t>0.3287,0.4413,0.3122,0.0122</t>
-  </si>
-  <si>
-    <t>0.0141,0.0343,0.9696,0.0063</t>
-  </si>
-  <si>
-    <t>0.0004,0.9291,0.8939,0.0000</t>
-  </si>
-  <si>
-    <t>0.0039,0.6897,0.9041,0.0007</t>
-  </si>
-  <si>
-    <t>0.0009,0.9890,0.0749,0.0003</t>
-  </si>
-  <si>
-    <t>0.0004,0.9779,0.4263,0.0012</t>
-  </si>
-  <si>
-    <t>0.0167,0.0011,0.0188,0.9743</t>
-  </si>
-  <si>
-    <t>0.0023,0.0452,0.0016,0.9971</t>
-  </si>
-  <si>
-    <t>0.0057,0.0109,0.0003,0.9971</t>
-  </si>
-  <si>
-    <t>0.0043,0.0010,0.0008,0.9975</t>
-  </si>
-  <si>
-    <t>0.0108,0.0174,0.1373,0.9432</t>
-  </si>
-  <si>
-    <t>0.0022,0.0051,0.0007,0.9982</t>
-  </si>
-  <si>
-    <t>0.0013,0.9352,0.6960,0.0004</t>
-  </si>
-  <si>
-    <t>0.0036,0.3259,0.9716,0.0006</t>
-  </si>
-  <si>
-    <t>0.0093,0.4111,0.7947,0.0005</t>
-  </si>
-  <si>
-    <t>0.0009,0.6646,0.9327,0.0004</t>
-  </si>
-  <si>
-    <t>0.0005,0.9468,0.8350,0.0000</t>
-  </si>
-  <si>
-    <t>0.0078,0.6804,0.8144,0.0008</t>
-  </si>
-  <si>
-    <t>0.9890,0.0028,0.0005,0.0026</t>
-  </si>
-  <si>
-    <t>0.9549,0.0390,0.0051,0.0071</t>
-  </si>
-  <si>
-    <t>0.9864,0.0069,0.0014,0.0020</t>
-  </si>
-  <si>
-    <t>0.9864,0.0087,0.0013,0.0013</t>
-  </si>
-  <si>
-    <t>0.9673,0.0209,0.0044,0.0058</t>
-  </si>
-  <si>
-    <t>0.9907,0.0030,0.0004,0.0016</t>
-  </si>
-  <si>
-    <t>0.9888,0.0063,0.0009,0.0012</t>
-  </si>
-  <si>
-    <t>0.9672,0.0416,0.0028,0.0009</t>
-  </si>
-  <si>
-    <t>0.9963,0.0006,0.0001,0.0008</t>
-  </si>
-  <si>
-    <t>0.9811,0.0191,0.0023,0.0006</t>
-  </si>
-  <si>
-    <t>0.9923,0.0013,0.0005,0.0028</t>
-  </si>
-  <si>
-    <t>0.9914,0.0062,0.0012,0.0005</t>
-  </si>
-  <si>
-    <t>0.9863,0.0051,0.0004,0.0034</t>
-  </si>
-  <si>
-    <t>0.9947,0.0014,0.0005,0.0009</t>
-  </si>
-  <si>
-    <t>0.9830,0.0057,0.0010,0.0046</t>
-  </si>
-  <si>
-    <t>0.9932,0.0031,0.0008,0.0005</t>
-  </si>
-  <si>
-    <t>0.0018,0.0034,0.9921,0.0042</t>
-  </si>
-  <si>
-    <t>0.0829,0.0049,0.9324,0.0059</t>
-  </si>
-  <si>
-    <t>0.5550,0.0331,0.3302,0.1288</t>
-  </si>
-  <si>
-    <t>0.2343,0.0065,0.8271,0.0095</t>
-  </si>
-  <si>
-    <t>0.0298,0.9637,0.0064,0.0005</t>
-  </si>
-  <si>
-    <t>0.0332,0.9594,0.0121,0.0004</t>
-  </si>
-  <si>
-    <t>0.0978,0.8982,0.0036,0.0070</t>
-  </si>
-  <si>
-    <t>0.4181,0.7047,0.0059,0.0007</t>
-  </si>
-  <si>
-    <t>0.1646,0.8705,0.0091,0.0020</t>
-  </si>
-  <si>
-    <t>0.0319,0.9587,0.0108,0.0002</t>
-  </si>
-  <si>
-    <t>0.3765,0.6849,0.0129,0.0016</t>
-  </si>
-  <si>
-    <t>0.5743,0.1270,0.3443,0.0620</t>
-  </si>
-  <si>
-    <t>0.3912,0.0081,0.7068,0.0074</t>
-  </si>
-  <si>
-    <t>0.5274,0.1034,0.4355,0.0108</t>
-  </si>
-  <si>
-    <t>0.2674,0.0551,0.7070,0.0325</t>
-  </si>
-  <si>
-    <t>0.5333,0.0628,0.0978,0.3192</t>
-  </si>
-  <si>
-    <t>0.0026,0.9902,0.0265,0.0007</t>
-  </si>
-  <si>
-    <t>0.0016,0.9869,0.0207,0.0084</t>
-  </si>
-  <si>
-    <t>0.1667,0.7495,0.2051,0.0696</t>
-  </si>
-  <si>
-    <t>0.0020,0.9708,0.4927,0.0018</t>
-  </si>
-  <si>
-    <t>0.0378,0.9414,0.1084,0.0021</t>
-  </si>
-  <si>
-    <t>0.8540,0.1549,0.0286,0.0074</t>
-  </si>
-  <si>
-    <t>0.7109,0.3609,0.0178,0.0010</t>
-  </si>
-  <si>
-    <t>0.9489,0.0264,0.0077,0.0154</t>
-  </si>
-  <si>
-    <t>0.9514,0.0176,0.0082,0.0188</t>
-  </si>
-  <si>
-    <t>0.9733,0.0024,0.0007,0.0196</t>
-  </si>
-  <si>
-    <t>0.9548,0.0094,0.0182,0.0092</t>
-  </si>
-  <si>
-    <t>0.9699,0.0050,0.0056,0.0091</t>
-  </si>
-  <si>
-    <t>0.9445,0.0339,0.0182,0.0038</t>
-  </si>
-  <si>
-    <t>0.9393,0.0129,0.0095,0.0240</t>
-  </si>
-  <si>
-    <t>0.9520,0.0197,0.0146,0.0110</t>
-  </si>
-  <si>
-    <t>0.0009,0.5630,0.9756,0.0002</t>
-  </si>
-  <si>
-    <t>0.0193,0.2848,0.8914,0.0005</t>
-  </si>
-  <si>
-    <t>0.0102,0.5707,0.8270,0.0010</t>
-  </si>
-  <si>
-    <t>0.0057,0.2415,0.9366,0.0006</t>
-  </si>
-  <si>
-    <t>0.3961,0.3619,0.1742,0.3116</t>
-  </si>
-  <si>
-    <t>0.7598,0.0327,0.1874,0.0232</t>
-  </si>
-  <si>
-    <t>0.4782,0.0103,0.5962,0.0117</t>
-  </si>
-  <si>
-    <t>0.5782,0.0605,0.3825,0.0091</t>
-  </si>
-  <si>
-    <t>0.0185,0.0084,0.0040,0.9872</t>
-  </si>
-  <si>
-    <t>0.0019,0.0016,0.0067,0.9948</t>
-  </si>
-  <si>
-    <t>0.0065,0.0033,0.0087,0.9901</t>
-  </si>
-  <si>
-    <t>0.0074,0.0013,0.0024,0.9944</t>
-  </si>
-  <si>
-    <t>0.0053,0.9346,0.4565,0.0031</t>
-  </si>
-  <si>
-    <t>0.9424,0.0323,0.0125,0.0088</t>
-  </si>
-  <si>
-    <t>0.1211,0.8565,0.0408,0.0112</t>
-  </si>
-  <si>
-    <t>0.9573,0.0190,0.0072,0.0091</t>
-  </si>
-  <si>
-    <t>0.8951,0.1045,0.0211,0.0042</t>
-  </si>
-  <si>
-    <t>0.9586,0.0052,0.0084,0.0135</t>
-  </si>
-  <si>
-    <t>0.1164,0.2423,0.0141,0.9019</t>
-  </si>
-  <si>
-    <t>0.9549,0.0235,0.0151,0.0026</t>
-  </si>
-  <si>
-    <t>0.0088,0.1781,0.7985,0.1925</t>
-  </si>
-  <si>
-    <t>0.6234,0.0074,0.0039,0.5428</t>
-  </si>
-  <si>
-    <t>0.8943,0.0204,0.0286,0.0470</t>
-  </si>
-  <si>
-    <t>0.1943,0.7934,0.0256,0.0257</t>
-  </si>
-  <si>
-    <t>0.8433,0.0940,0.0439,0.0137</t>
-  </si>
-  <si>
-    <t>0.8141,0.1398,0.0643,0.0038</t>
-  </si>
-  <si>
-    <t>0.4736,0.5029,0.0457,0.0544</t>
-  </si>
-  <si>
-    <t>0.7912,0.0317,0.0850,0.0846</t>
-  </si>
-  <si>
-    <t>0.8038,0.1628,0.0374,0.0257</t>
-  </si>
-  <si>
-    <t>0.9849,0.0027,0.0019,0.0054</t>
-  </si>
-  <si>
-    <t>0.9722,0.0176,0.0026,0.0038</t>
-  </si>
-  <si>
-    <t>0.9783,0.0021,0.0044,0.0075</t>
-  </si>
-  <si>
-    <t>0.9770,0.0007,0.0007,0.0174</t>
-  </si>
-  <si>
-    <t>0.9825,0.0044,0.0023,0.0050</t>
-  </si>
-  <si>
-    <t>0.9295,0.0881,0.0085,0.0019</t>
-  </si>
-  <si>
-    <t>0.9787,0.0090,0.0018,0.0058</t>
-  </si>
-  <si>
-    <t>0.9786,0.0050,0.0018,0.0102</t>
-  </si>
-  <si>
-    <t>0.5810,0.4633,0.0095,0.0088</t>
-  </si>
-  <si>
-    <t>0.5813,0.4940,0.0230,0.0009</t>
-  </si>
-  <si>
-    <t>0.7313,0.3936,0.0054,0.0007</t>
-  </si>
-  <si>
-    <t>0.4343,0.1433,0.5764,0.0128</t>
-  </si>
-  <si>
-    <t>0.9305,0.0684,0.0119,0.0032</t>
-  </si>
-  <si>
-    <t>0.8569,0.1045,0.0469,0.0192</t>
-  </si>
-  <si>
-    <t>0.9484,0.0206,0.0252,0.0017</t>
-  </si>
-  <si>
-    <t>0.8290,0.2247,0.0118,0.0034</t>
-  </si>
-  <si>
-    <t>0.0078,0.0174,0.9879,0.0021</t>
-  </si>
-  <si>
-    <t>0.9355,0.0601,0.0117,0.0034</t>
-  </si>
-  <si>
-    <t>0.0035,0.0067,0.9896,0.0031</t>
-  </si>
-  <si>
-    <t>0.0018,0.1170,0.9817,0.0040</t>
-  </si>
-  <si>
-    <t>0.0504,0.0094,0.9460,0.0061</t>
-  </si>
-  <si>
-    <t>0.0065,0.0677,0.9798,0.0011</t>
-  </si>
-  <si>
-    <t>0.0121,0.0619,0.9649,0.0030</t>
-  </si>
-  <si>
-    <t>0.0268,0.0016,0.9815,0.0008</t>
-  </si>
-  <si>
-    <t>0.0060,0.0122,0.9880,0.0013</t>
-  </si>
-  <si>
-    <t>0.4251,0.0798,0.5489,0.0245</t>
-  </si>
-  <si>
-    <t>0.1456,0.0092,0.8893,0.0031</t>
-  </si>
-  <si>
-    <t>0.4817,0.0585,0.5123,0.0079</t>
-  </si>
-  <si>
-    <t>0.4113,0.2201,0.4096,0.0147</t>
-  </si>
-  <si>
-    <t>0.0590,0.8232,0.2403,0.0033</t>
-  </si>
-  <si>
-    <t>0.5417,0.1850,0.3621,0.0556</t>
-  </si>
-  <si>
-    <t>0.3705,0.0751,0.5970,0.0209</t>
-  </si>
-  <si>
-    <t>0.5100,0.0702,0.4777,0.0204</t>
-  </si>
-  <si>
-    <t>0.7674,0.3486,0.0094,0.0010</t>
-  </si>
-  <si>
-    <t>0.5836,0.5856,0.0053,0.0004</t>
-  </si>
-  <si>
-    <t>0.6803,0.5284,0.0016,0.0002</t>
-  </si>
-  <si>
-    <t>0.9772,0.0136,0.0049,0.0019</t>
-  </si>
-  <si>
-    <t>0.9603,0.0397,0.0070,0.0019</t>
-  </si>
-  <si>
-    <t>0.5927,0.1848,0.2860,0.0762</t>
-  </si>
-  <si>
-    <t>0.8328,0.0182,0.1253,0.0108</t>
-  </si>
-  <si>
-    <t>0.5377,0.0115,0.1426,0.2516</t>
-  </si>
-  <si>
-    <t>0.4985,0.0208,0.5543,0.0089</t>
-  </si>
-  <si>
-    <t>0.5771,0.0066,0.5168,0.0095</t>
-  </si>
-  <si>
-    <t>0.0170,0.0117,0.9725,0.0040</t>
-  </si>
-  <si>
-    <t>0.0461,0.4354,0.7089,0.0084</t>
-  </si>
-  <si>
-    <t>0.0199,0.1430,0.9171,0.0259</t>
-  </si>
-  <si>
-    <t>0.1108,0.2299,0.7307,0.0446</t>
-  </si>
-  <si>
-    <t>0.0548,0.2424,0.7826,0.0149</t>
-  </si>
-  <si>
-    <t>0.9868,0.0051,0.0017,0.0029</t>
-  </si>
-  <si>
-    <t>0.9857,0.0049,0.0015,0.0042</t>
-  </si>
-  <si>
-    <t>0.9901,0.0045,0.0006,0.0014</t>
-  </si>
-  <si>
-    <t>0.9778,0.0178,0.0034,0.0015</t>
-  </si>
-  <si>
-    <t>0.9786,0.0167,0.0037,0.0009</t>
-  </si>
-  <si>
-    <t>0.9797,0.0158,0.0028,0.0014</t>
-  </si>
-  <si>
-    <t>0.9844,0.0018,0.0002,0.0072</t>
-  </si>
-  <si>
-    <t>0.9764,0.0064,0.0014,0.0085</t>
-  </si>
-  <si>
-    <t>0.4951,0.0164,0.5883,0.0144</t>
-  </si>
-  <si>
-    <t>0.2516,0.4259,0.4749,0.0372</t>
-  </si>
-  <si>
-    <t>0.9279,0.0150,0.0152,0.0329</t>
-  </si>
-  <si>
-    <t>0.0066,0.0051,0.9886,0.0018</t>
-  </si>
-  <si>
-    <t>0.0003,0.0047,0.9979,0.0007</t>
-  </si>
-  <si>
-    <t>0.0099,0.0521,0.9713,0.0007</t>
-  </si>
-  <si>
-    <t>0.0004,0.0018,0.9978,0.0011</t>
-  </si>
-  <si>
-    <t>0.0615,0.0070,0.9462,0.0030</t>
-  </si>
-  <si>
-    <t>0.0009,0.0033,0.9953,0.0016</t>
-  </si>
-  <si>
-    <t>0.0128,0.0431,0.9684,0.0074</t>
-  </si>
-  <si>
-    <t>0.2063,0.0491,0.7572,0.0135</t>
-  </si>
-  <si>
-    <t>0.6583,0.0065,0.3142,0.0195</t>
-  </si>
-  <si>
-    <t>0.5185,0.0048,0.5767,0.0118</t>
-  </si>
-  <si>
-    <t>0.5434,0.0124,0.3265,0.0797</t>
-  </si>
-  <si>
-    <t>0.9903,0.0059,0.0013,0.0006</t>
-  </si>
-  <si>
-    <t>0.9875,0.0086,0.0014,0.0011</t>
-  </si>
-  <si>
-    <t>0.9865,0.0061,0.0020,0.0016</t>
-  </si>
-  <si>
-    <t>0.9728,0.0217,0.0044,0.0014</t>
-  </si>
-  <si>
-    <t>0.9861,0.0058,0.0019,0.0028</t>
-  </si>
-  <si>
-    <t>0.9572,0.0363,0.0091,0.0005</t>
-  </si>
-  <si>
-    <t>0.9871,0.0083,0.0017,0.0013</t>
-  </si>
-  <si>
-    <t>0.9602,0.0248,0.0032,0.0071</t>
-  </si>
-  <si>
-    <t>0.0342,0.0662,0.8973,0.0014</t>
-  </si>
-  <si>
-    <t>0.0083,0.0153,0.9821,0.0029</t>
-  </si>
-  <si>
-    <t>0.0141,0.0130,0.9799,0.0012</t>
-  </si>
-  <si>
-    <t>0.0597,0.0461,0.9008,0.0102</t>
-  </si>
-  <si>
-    <t>0.0010,0.0017,0.9934,0.0070</t>
-  </si>
-  <si>
-    <t>0.3228,0.0189,0.5386,0.1479</t>
-  </si>
-  <si>
-    <t>0.3132,0.0290,0.6526,0.0516</t>
-  </si>
-  <si>
-    <t>0.0611,0.0183,0.9049,0.0362</t>
-  </si>
-  <si>
-    <t>0.5404,0.0045,0.0153,0.5528</t>
-  </si>
-  <si>
-    <t>0.0398,0.1255,0.0116,0.9699</t>
-  </si>
-  <si>
-    <t>0.0076,0.0006,0.0010,0.9957</t>
-  </si>
-  <si>
-    <t>0.0082,0.0004,0.0026,0.9936</t>
-  </si>
-  <si>
-    <t>0.0049,0.0014,0.0011,0.9969</t>
-  </si>
-  <si>
-    <t>0.3825,0.0956,0.0114,0.6808</t>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0.7705,0.1608,0.0698,0.0187</t>
+  </si>
+  <si>
+    <t>0.0151,0.0089,0.0004,0.9932</t>
+  </si>
+  <si>
+    <t>0.1504,0.0162,0.0166,0.9192</t>
+  </si>
+  <si>
+    <t>0.1899,0.0132,0.0007,0.9333</t>
+  </si>
+  <si>
+    <t>0.9896,0.0033,0.0016,0.0015</t>
+  </si>
+  <si>
+    <t>0.9936,0.0032,0.0006,0.0006</t>
+  </si>
+  <si>
+    <t>0.9758,0.0111,0.0039,0.0059</t>
+  </si>
+  <si>
+    <t>0.9856,0.0064,0.0024,0.0025</t>
+  </si>
+  <si>
+    <t>0.9869,0.0042,0.0005,0.0033</t>
+  </si>
+  <si>
+    <t>0.9923,0.0034,0.0009,0.0011</t>
+  </si>
+  <si>
+    <t>0.9860,0.0047,0.0011,0.0031</t>
+  </si>
+  <si>
+    <t>0.9939,0.0023,0.0004,0.0009</t>
+  </si>
+  <si>
+    <t>0.6943,0.0234,0.2913,0.0303</t>
+  </si>
+  <si>
+    <t>0.2451,0.0147,0.7929,0.0163</t>
+  </si>
+  <si>
+    <t>0.1398,0.0221,0.8704,0.0022</t>
+  </si>
+  <si>
+    <t>0.2770,0.0049,0.8133,0.0042</t>
+  </si>
+  <si>
+    <t>0.2931,0.1396,0.5960,0.0160</t>
+  </si>
+  <si>
+    <t>0.0191,0.9747,0.0012,0.0010</t>
+  </si>
+  <si>
+    <t>0.0881,0.9359,0.0050,0.0003</t>
+  </si>
+  <si>
+    <t>0.6226,0.4502,0.0193,0.0087</t>
+  </si>
+  <si>
+    <t>0.2670,0.8269,0.0036,0.0004</t>
+  </si>
+  <si>
+    <t>0.0040,0.9940,0.0015,0.0001</t>
+  </si>
+  <si>
+    <t>0.3873,0.1603,0.3558,0.2705</t>
+  </si>
+  <si>
+    <t>0.4467,0.0734,0.4367,0.1448</t>
+  </si>
+  <si>
+    <t>0.0631,0.0061,0.9478,0.0027</t>
+  </si>
+  <si>
+    <t>0.4429,0.0091,0.5349,0.0416</t>
+  </si>
+  <si>
+    <t>0.0562,0.0035,0.9298,0.0196</t>
+  </si>
+  <si>
+    <t>0.0449,0.0090,0.9487,0.0055</t>
+  </si>
+  <si>
+    <t>0.0054,0.0026,0.9744,0.0253</t>
+  </si>
+  <si>
+    <t>0.2411,0.7770,0.0227,0.0015</t>
+  </si>
+  <si>
+    <t>0.5330,0.2918,0.2531,0.0251</t>
+  </si>
+  <si>
+    <t>0.0007,0.0032,0.9929,0.0087</t>
+  </si>
+  <si>
+    <t>0.0394,0.8139,0.2119,0.0039</t>
+  </si>
+  <si>
+    <t>0.7518,0.1876,0.0823,0.0342</t>
+  </si>
+  <si>
+    <t>0.8072,0.0765,0.1084,0.0061</t>
+  </si>
+  <si>
+    <t>0.6765,0.3130,0.0388,0.0012</t>
+  </si>
+  <si>
+    <t>0.2612,0.7305,0.1323,0.0071</t>
+  </si>
+  <si>
+    <t>0.0325,0.3272,0.5346,0.2022</t>
+  </si>
+  <si>
+    <t>0.0871,0.1842,0.8030,0.0199</t>
+  </si>
+  <si>
+    <t>0.1876,0.2970,0.6026,0.0674</t>
+  </si>
+  <si>
+    <t>0.1108,0.0649,0.8155,0.0651</t>
+  </si>
+  <si>
+    <t>0.0082,0.0142,0.9891,0.0002</t>
+  </si>
+  <si>
+    <t>0.0082,0.9490,0.1191,0.0030</t>
+  </si>
+  <si>
+    <t>0.0843,0.0722,0.8877,0.0078</t>
+  </si>
+  <si>
+    <t>0.1277,0.6570,0.0473,0.6662</t>
+  </si>
+  <si>
+    <t>0.0022,0.9855,0.0391,0.0060</t>
+  </si>
+  <si>
+    <t>0.0032,0.9694,0.3469,0.0014</t>
+  </si>
+  <si>
+    <t>0.0020,0.9813,0.2210,0.0039</t>
+  </si>
+  <si>
+    <t>0.0063,0.0703,0.9775,0.0031</t>
+  </si>
+  <si>
+    <t>0.0014,0.0255,0.9928,0.0018</t>
+  </si>
+  <si>
+    <t>0.1455,0.0735,0.7818,0.0550</t>
+  </si>
+  <si>
+    <t>0.0315,0.0027,0.9742,0.0011</t>
+  </si>
+  <si>
+    <t>0.0165,0.0230,0.9725,0.0033</t>
+  </si>
+  <si>
+    <t>0.0056,0.0221,0.9802,0.0034</t>
+  </si>
+  <si>
+    <t>0.9540,0.0631,0.0043,0.0013</t>
+  </si>
+  <si>
+    <t>0.9810,0.0104,0.0036,0.0016</t>
+  </si>
+  <si>
+    <t>0.9684,0.0124,0.0077,0.0071</t>
+  </si>
+  <si>
+    <t>0.0117,0.0950,0.9747,0.0069</t>
+  </si>
+  <si>
+    <t>0.9582,0.0225,0.0075,0.0134</t>
+  </si>
+  <si>
+    <t>0.9725,0.0339,0.0032,0.0006</t>
+  </si>
+  <si>
+    <t>0.9307,0.0655,0.0135,0.0070</t>
+  </si>
+  <si>
+    <t>0.0006,0.9391,0.8184,0.0001</t>
+  </si>
+  <si>
+    <t>0.0051,0.2471,0.9646,0.0053</t>
+  </si>
+  <si>
+    <t>0.0037,0.3973,0.8228,0.0309</t>
+  </si>
+  <si>
+    <t>0.0013,0.8083,0.9405,0.0006</t>
+  </si>
+  <si>
+    <t>0.0020,0.0074,0.9953,0.0005</t>
+  </si>
+  <si>
+    <t>0.0739,0.9110,0.0135,0.0058</t>
+  </si>
+  <si>
+    <t>0.0246,0.9767,0.0010,0.0001</t>
+  </si>
+  <si>
+    <t>0.8280,0.0724,0.0954,0.0078</t>
+  </si>
+  <si>
+    <t>0.4754,0.4467,0.1893,0.0351</t>
+  </si>
+  <si>
+    <t>0.0162,0.0318,0.9636,0.0137</t>
+  </si>
+  <si>
+    <t>0.0058,0.7638,0.8495,0.0008</t>
+  </si>
+  <si>
+    <t>0.0002,0.9906,0.3134,0.0000</t>
+  </si>
+  <si>
+    <t>0.0014,0.9873,0.0997,0.0001</t>
+  </si>
+  <si>
+    <t>0.0010,0.9313,0.7627,0.0017</t>
+  </si>
+  <si>
+    <t>0.0086,0.0009,0.1205,0.9313</t>
+  </si>
+  <si>
+    <t>0.0019,0.0018,0.0003,0.9987</t>
+  </si>
+  <si>
+    <t>0.0041,0.0018,0.0003,0.9979</t>
+  </si>
+  <si>
+    <t>0.0056,0.0043,0.0007,0.9968</t>
+  </si>
+  <si>
+    <t>0.0086,0.0029,0.0600,0.9693</t>
+  </si>
+  <si>
+    <t>0.0018,0.0087,0.0001,0.9989</t>
+  </si>
+  <si>
+    <t>0.0001,0.9889,0.4994,0.0001</t>
+  </si>
+  <si>
+    <t>0.0011,0.7236,0.9663,0.0003</t>
+  </si>
+  <si>
+    <t>0.0090,0.4640,0.8790,0.0032</t>
+  </si>
+  <si>
+    <t>0.0065,0.0639,0.9681,0.0064</t>
+  </si>
+  <si>
+    <t>0.0009,0.9836,0.2571,0.0002</t>
+  </si>
+  <si>
+    <t>0.0028,0.8465,0.8399,0.0003</t>
+  </si>
+  <si>
+    <t>0.9868,0.0103,0.0018,0.0007</t>
+  </si>
+  <si>
+    <t>0.9664,0.0286,0.0059,0.0013</t>
+  </si>
+  <si>
+    <t>0.9606,0.0565,0.0035,0.0003</t>
+  </si>
+  <si>
+    <t>0.9831,0.0084,0.0016,0.0030</t>
+  </si>
+  <si>
+    <t>0.9736,0.0249,0.0039,0.0012</t>
+  </si>
+  <si>
+    <t>0.9880,0.0039,0.0012,0.0021</t>
+  </si>
+  <si>
+    <t>0.9833,0.0063,0.0010,0.0042</t>
+  </si>
+  <si>
+    <t>0.9866,0.0096,0.0014,0.0008</t>
+  </si>
+  <si>
+    <t>0.9925,0.0025,0.0006,0.0014</t>
+  </si>
+  <si>
+    <t>0.9936,0.0030,0.0009,0.0006</t>
+  </si>
+  <si>
+    <t>0.9945,0.0015,0.0003,0.0013</t>
+  </si>
+  <si>
+    <t>0.9945,0.0008,0.0001,0.0019</t>
+  </si>
+  <si>
+    <t>0.9959,0.0011,0.0003,0.0007</t>
+  </si>
+  <si>
+    <t>0.9940,0.0026,0.0003,0.0010</t>
+  </si>
+  <si>
+    <t>0.9916,0.0042,0.0007,0.0008</t>
+  </si>
+  <si>
+    <t>0.9905,0.0045,0.0010,0.0013</t>
+  </si>
+  <si>
+    <t>0.0123,0.0049,0.9789,0.0053</t>
+  </si>
+  <si>
+    <t>0.0433,0.0519,0.9369,0.0023</t>
+  </si>
+  <si>
+    <t>0.4289,0.0296,0.5983,0.0354</t>
+  </si>
+  <si>
+    <t>0.0074,0.0011,0.9882,0.0036</t>
+  </si>
+  <si>
+    <t>0.0177,0.9782,0.0011,0.0009</t>
+  </si>
+  <si>
+    <t>0.0416,0.9549,0.0078,0.0017</t>
+  </si>
+  <si>
+    <t>0.3778,0.6487,0.0038,0.0081</t>
+  </si>
+  <si>
+    <t>0.1222,0.9040,0.0035,0.0008</t>
+  </si>
+  <si>
+    <t>0.0688,0.9411,0.0052,0.0007</t>
+  </si>
+  <si>
+    <t>0.0376,0.9647,0.0063,0.0002</t>
+  </si>
+  <si>
+    <t>0.7458,0.3227,0.0164,0.0019</t>
+  </si>
+  <si>
+    <t>0.6044,0.0681,0.3618,0.0541</t>
+  </si>
+  <si>
+    <t>0.2992,0.0103,0.7750,0.0031</t>
+  </si>
+  <si>
+    <t>0.4051,0.3457,0.2989,0.1718</t>
+  </si>
+  <si>
+    <t>0.4631,0.0596,0.5396,0.0259</t>
+  </si>
+  <si>
+    <t>0.0681,0.0549,0.0464,0.9363</t>
+  </si>
+  <si>
+    <t>0.0015,0.9924,0.0396,0.0007</t>
+  </si>
+  <si>
+    <t>0.0033,0.9782,0.1142,0.0042</t>
+  </si>
+  <si>
+    <t>0.0399,0.9273,0.0140,0.0750</t>
+  </si>
+  <si>
+    <t>0.0001,0.9118,0.9806,0.0001</t>
+  </si>
+  <si>
+    <t>0.0458,0.9466,0.0604,0.0016</t>
+  </si>
+  <si>
+    <t>0.7628,0.2630,0.0360,0.0025</t>
+  </si>
+  <si>
+    <t>0.8433,0.1905,0.0182,0.0012</t>
+  </si>
+  <si>
+    <t>0.9507,0.0119,0.0061,0.0341</t>
+  </si>
+  <si>
+    <t>0.9518,0.0180,0.0089,0.0132</t>
+  </si>
+  <si>
+    <t>0.9765,0.0127,0.0045,0.0025</t>
+  </si>
+  <si>
+    <t>0.9449,0.0168,0.0197,0.0144</t>
+  </si>
+  <si>
+    <t>0.9683,0.0131,0.0030,0.0115</t>
+  </si>
+  <si>
+    <t>0.9272,0.0495,0.0284,0.0052</t>
+  </si>
+  <si>
+    <t>0.9764,0.0065,0.0054,0.0068</t>
+  </si>
+  <si>
+    <t>0.9807,0.0049,0.0038,0.0042</t>
+  </si>
+  <si>
+    <t>0.0030,0.8911,0.7499,0.0004</t>
+  </si>
+  <si>
+    <t>0.0034,0.7175,0.8671,0.0004</t>
+  </si>
+  <si>
+    <t>0.0147,0.5633,0.7509,0.0022</t>
+  </si>
+  <si>
+    <t>0.0019,0.7219,0.7891,0.0001</t>
+  </si>
+  <si>
+    <t>0.5949,0.1298,0.2296,0.1028</t>
+  </si>
+  <si>
+    <t>0.5149,0.3664,0.1458,0.0632</t>
+  </si>
+  <si>
+    <t>0.1136,0.0021,0.9330,0.0068</t>
+  </si>
+  <si>
+    <t>0.4091,0.3162,0.2337,0.1458</t>
+  </si>
+  <si>
+    <t>0.0264,0.0051,0.0008,0.9906</t>
+  </si>
+  <si>
+    <t>0.0006,0.0016,0.0002,0.9993</t>
+  </si>
+  <si>
+    <t>0.0012,0.0064,0.0002,0.9991</t>
+  </si>
+  <si>
+    <t>0.0111,0.0014,0.0031,0.9917</t>
+  </si>
+  <si>
+    <t>0.0014,0.9541,0.5050,0.0008</t>
+  </si>
+  <si>
+    <t>0.9616,0.0390,0.0057,0.0012</t>
+  </si>
+  <si>
+    <t>0.6794,0.3520,0.0145,0.0131</t>
+  </si>
+  <si>
+    <t>0.9431,0.0129,0.0166,0.0167</t>
+  </si>
+  <si>
+    <t>0.8003,0.2115,0.0362,0.0032</t>
+  </si>
+  <si>
+    <t>0.9633,0.0025,0.0043,0.0147</t>
+  </si>
+  <si>
+    <t>0.6551,0.0412,0.0316,0.3538</t>
+  </si>
+  <si>
+    <t>0.9821,0.0043,0.0048,0.0027</t>
+  </si>
+  <si>
+    <t>0.0091,0.0383,0.9451,0.0743</t>
+  </si>
+  <si>
+    <t>0.8063,0.0023,0.0080,0.1912</t>
+  </si>
+  <si>
+    <t>0.9083,0.0052,0.0027,0.0827</t>
+  </si>
+  <si>
+    <t>0.6115,0.3832,0.0299,0.0289</t>
+  </si>
+  <si>
+    <t>0.6828,0.2768,0.0337,0.0281</t>
+  </si>
+  <si>
+    <t>0.8858,0.0714,0.0376,0.0043</t>
+  </si>
+  <si>
+    <t>0.3976,0.5004,0.1596,0.0776</t>
+  </si>
+  <si>
+    <t>0.8031,0.0670,0.1454,0.0043</t>
+  </si>
+  <si>
+    <t>0.4568,0.4588,0.1500,0.0069</t>
+  </si>
+  <si>
+    <t>0.9834,0.0046,0.0027,0.0031</t>
+  </si>
+  <si>
+    <t>0.9876,0.0015,0.0003,0.0068</t>
+  </si>
+  <si>
+    <t>0.9788,0.0014,0.0025,0.0090</t>
+  </si>
+  <si>
+    <t>0.9803,0.0039,0.0015,0.0088</t>
+  </si>
+  <si>
+    <t>0.9681,0.0119,0.0081,0.0091</t>
+  </si>
+  <si>
+    <t>0.9737,0.0148,0.0026,0.0059</t>
+  </si>
+  <si>
+    <t>0.9527,0.0056,0.0018,0.0355</t>
+  </si>
+  <si>
+    <t>0.9800,0.0105,0.0032,0.0020</t>
+  </si>
+  <si>
+    <t>0.3732,0.6999,0.0207,0.0080</t>
+  </si>
+  <si>
+    <t>0.8147,0.2157,0.0238,0.0017</t>
+  </si>
+  <si>
+    <t>0.6800,0.4002,0.0167,0.0007</t>
+  </si>
+  <si>
+    <t>0.6996,0.1470,0.1876,0.0243</t>
+  </si>
+  <si>
+    <t>0.9761,0.0134,0.0060,0.0015</t>
+  </si>
+  <si>
+    <t>0.9026,0.0553,0.0144,0.0282</t>
+  </si>
+  <si>
+    <t>0.9813,0.0094,0.0036,0.0021</t>
+  </si>
+  <si>
+    <t>0.9191,0.0837,0.0122,0.0017</t>
+  </si>
+  <si>
+    <t>0.0009,0.0505,0.9945,0.0011</t>
+  </si>
+  <si>
+    <t>0.9528,0.0374,0.0148,0.0025</t>
+  </si>
+  <si>
+    <t>0.0027,0.0140,0.9904,0.0019</t>
+  </si>
+  <si>
+    <t>0.0183,0.2328,0.9083,0.0222</t>
+  </si>
+  <si>
+    <t>0.0344,0.0355,0.9546,0.0052</t>
+  </si>
+  <si>
+    <t>0.0796,0.4553,0.7054,0.0145</t>
+  </si>
+  <si>
+    <t>0.0063,0.0024,0.9927,0.0008</t>
+  </si>
+  <si>
+    <t>0.0230,0.0028,0.9793,0.0021</t>
+  </si>
+  <si>
+    <t>0.0021,0.0040,0.9964,0.0004</t>
+  </si>
+  <si>
+    <t>0.4021,0.0549,0.5835,0.0115</t>
+  </si>
+  <si>
+    <t>0.4722,0.1314,0.4702,0.0671</t>
+  </si>
+  <si>
+    <t>0.5639,0.0286,0.4555,0.0117</t>
+  </si>
+  <si>
+    <t>0.2008,0.4401,0.4590,0.0113</t>
+  </si>
+  <si>
+    <t>0.2619,0.0767,0.7160,0.0056</t>
+  </si>
+  <si>
+    <t>0.2534,0.0163,0.7746,0.0011</t>
+  </si>
+  <si>
+    <t>0.3835,0.1386,0.5052,0.0370</t>
+  </si>
+  <si>
+    <t>0.3476,0.1558,0.5278,0.0438</t>
+  </si>
+  <si>
+    <t>0.6182,0.5190,0.0122,0.0009</t>
+  </si>
+  <si>
+    <t>0.2869,0.8037,0.0028,0.0007</t>
+  </si>
+  <si>
+    <t>0.9425,0.0826,0.0043,0.0004</t>
+  </si>
+  <si>
+    <t>0.9349,0.0676,0.0040,0.0062</t>
+  </si>
+  <si>
+    <t>0.8828,0.1634,0.0079,0.0008</t>
+  </si>
+  <si>
+    <t>0.6409,0.1942,0.1930,0.0446</t>
+  </si>
+  <si>
+    <t>0.6921,0.0351,0.3207,0.0098</t>
+  </si>
+  <si>
+    <t>0.6875,0.0392,0.2882,0.0216</t>
+  </si>
+  <si>
+    <t>0.5491,0.0977,0.4070,0.0495</t>
+  </si>
+  <si>
+    <t>0.4005,0.1294,0.5330,0.0519</t>
+  </si>
+  <si>
+    <t>0.0165,0.0098,0.9298,0.0988</t>
+  </si>
+  <si>
+    <t>0.0058,0.0380,0.9752,0.0057</t>
+  </si>
+  <si>
+    <t>0.0260,0.1398,0.9284,0.0132</t>
+  </si>
+  <si>
+    <t>0.0693,0.0270,0.8608,0.0646</t>
+  </si>
+  <si>
+    <t>0.0029,0.3811,0.9505,0.0009</t>
+  </si>
+  <si>
+    <t>0.9799,0.0078,0.0005,0.0058</t>
+  </si>
+  <si>
+    <t>0.9689,0.0238,0.0060,0.0019</t>
+  </si>
+  <si>
+    <t>0.9851,0.0067,0.0024,0.0025</t>
+  </si>
+  <si>
+    <t>0.9838,0.0108,0.0025,0.0010</t>
+  </si>
+  <si>
+    <t>0.9769,0.0224,0.0018,0.0018</t>
+  </si>
+  <si>
+    <t>0.9738,0.0052,0.0018,0.0126</t>
+  </si>
+  <si>
+    <t>0.9885,0.0071,0.0020,0.0008</t>
+  </si>
+  <si>
+    <t>0.9915,0.0028,0.0006,0.0014</t>
+  </si>
+  <si>
+    <t>0.1135,0.0114,0.8514,0.0551</t>
+  </si>
+  <si>
+    <t>0.6262,0.2202,0.2598,0.0361</t>
+  </si>
+  <si>
+    <t>0.8518,0.0537,0.0526,0.0508</t>
+  </si>
+  <si>
+    <t>0.0035,0.0030,0.9915,0.0023</t>
+  </si>
+  <si>
+    <t>0.0156,0.1927,0.9340,0.0089</t>
+  </si>
+  <si>
+    <t>0.0231,0.0456,0.9451,0.0004</t>
+  </si>
+  <si>
+    <t>0.0007,0.0074,0.9898,0.0109</t>
+  </si>
+  <si>
+    <t>0.1956,0.0411,0.7707,0.0031</t>
+  </si>
+  <si>
+    <t>0.0008,0.0056,0.9975,0.0004</t>
+  </si>
+  <si>
+    <t>0.0146,0.0025,0.9872,0.0012</t>
+  </si>
+  <si>
+    <t>0.0246,0.0497,0.9515,0.0063</t>
+  </si>
+  <si>
+    <t>0.4685,0.0348,0.4711,0.0839</t>
+  </si>
+  <si>
+    <t>0.4014,0.0272,0.6248,0.0121</t>
+  </si>
+  <si>
+    <t>0.7359,0.0141,0.2353,0.0299</t>
+  </si>
+  <si>
+    <t>0.9826,0.0087,0.0014,0.0038</t>
+  </si>
+  <si>
+    <t>0.9905,0.0060,0.0015,0.0005</t>
+  </si>
+  <si>
+    <t>0.9949,0.0016,0.0007,0.0007</t>
+  </si>
+  <si>
+    <t>0.9796,0.0153,0.0025,0.0010</t>
+  </si>
+  <si>
+    <t>0.9600,0.0105,0.0014,0.0165</t>
+  </si>
+  <si>
+    <t>0.9882,0.0076,0.0015,0.0008</t>
+  </si>
+  <si>
+    <t>0.9829,0.0128,0.0012,0.0012</t>
+  </si>
+  <si>
+    <t>0.9867,0.0044,0.0019,0.0022</t>
+  </si>
+  <si>
+    <t>0.0269,0.0387,0.9443,0.0032</t>
+  </si>
+  <si>
+    <t>0.0013,0.1569,0.9825,0.0014</t>
+  </si>
+  <si>
+    <t>0.0024,0.0148,0.9866,0.0070</t>
+  </si>
+  <si>
+    <t>0.0764,0.0999,0.8203,0.0073</t>
+  </si>
+  <si>
+    <t>0.0053,0.0018,0.9843,0.0122</t>
+  </si>
+  <si>
+    <t>0.3231,0.0234,0.3075,0.3517</t>
+  </si>
+  <si>
+    <t>0.1232,0.0778,0.6935,0.1600</t>
+  </si>
+  <si>
+    <t>0.0495,0.2517,0.7894,0.0859</t>
+  </si>
+  <si>
+    <t>0.4872,0.0008,0.0037,0.6852</t>
+  </si>
+  <si>
+    <t>0.1472,0.0121,0.0370,0.8831</t>
+  </si>
+  <si>
+    <t>0.0241,0.0663,0.0037,0.9833</t>
+  </si>
+  <si>
+    <t>0.0052,0.0002,0.0015,0.9952</t>
+  </si>
+  <si>
+    <t>0.0093,0.0027,0.0012,0.9952</t>
+  </si>
+  <si>
+    <t>0.7531,0.0518,0.0687,0.1582</t>
   </si>
 </sst>
 </file>
@@ -1959,7 +1965,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1973,7 +1979,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1984,10 +1990,10 @@
         <v>259</v>
       </c>
       <c r="C4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2001,7 +2007,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2015,7 +2021,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2029,7 +2035,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2043,7 +2049,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2057,7 +2063,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2071,7 +2077,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2085,7 +2091,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2099,7 +2105,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2113,7 +2119,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2127,7 +2133,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2141,7 +2147,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2155,7 +2161,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2169,7 +2175,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2183,7 +2189,7 @@
         <v>261</v>
       </c>
       <c r="D18" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2197,7 +2203,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2211,7 +2217,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2225,7 +2231,7 @@
         <v>259</v>
       </c>
       <c r="D21" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2239,7 +2245,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2253,7 +2259,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2264,10 +2270,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D24" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2278,10 +2284,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D25" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2295,7 +2301,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2309,7 +2315,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2323,7 +2329,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2337,7 +2343,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2351,7 +2357,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2362,10 +2368,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2379,7 +2385,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2393,7 +2399,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2407,7 +2413,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2421,7 +2427,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2435,7 +2441,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2449,7 +2455,7 @@
         <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2463,7 +2469,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2474,10 +2480,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D39" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2491,7 +2497,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2505,7 +2511,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2519,7 +2525,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2533,7 +2539,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2547,7 +2553,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2561,7 +2567,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2572,10 +2578,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D46" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2589,7 +2595,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2603,7 +2609,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2617,7 +2623,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2631,7 +2637,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2645,7 +2651,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2659,7 +2665,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2673,7 +2679,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2687,7 +2693,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2701,7 +2707,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2715,7 +2721,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2729,7 +2735,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2743,7 +2749,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2757,7 +2763,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2771,7 +2777,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2785,7 +2791,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2799,7 +2805,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2810,10 +2816,10 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2827,7 +2833,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2841,7 +2847,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2855,7 +2861,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2869,7 +2875,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2883,7 +2889,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2897,7 +2903,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2911,7 +2917,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2922,10 +2928,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D71" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2939,7 +2945,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2953,7 +2959,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2964,10 +2970,10 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D74" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2981,7 +2987,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2992,10 +2998,10 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3009,7 +3015,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3023,7 +3029,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3037,7 +3043,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3051,7 +3057,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3065,7 +3071,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3079,7 +3085,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3090,10 +3096,10 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D83" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3104,10 +3110,10 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3121,7 +3127,7 @@
         <v>261</v>
       </c>
       <c r="D85" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3132,10 +3138,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3146,10 +3152,10 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D87" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3163,7 +3169,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3177,7 +3183,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3191,7 +3197,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3205,7 +3211,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3219,7 +3225,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3233,7 +3239,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3247,7 +3253,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3261,7 +3267,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3275,7 +3281,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3289,7 +3295,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3303,7 +3309,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3317,7 +3323,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3331,7 +3337,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3345,7 +3351,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3359,7 +3365,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3373,7 +3379,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3387,7 +3393,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3401,7 +3407,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3415,7 +3421,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3426,10 +3432,10 @@
         <v>259</v>
       </c>
       <c r="C107" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D107" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3443,7 +3449,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3457,7 +3463,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3471,7 +3477,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3485,7 +3491,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3499,7 +3505,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3513,7 +3519,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3527,7 +3533,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3538,10 +3544,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3555,7 +3561,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3569,7 +3575,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3580,10 +3586,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D118" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3597,7 +3603,7 @@
         <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3608,10 +3614,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3625,7 +3631,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3639,7 +3645,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3653,7 +3659,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3664,10 +3670,10 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3681,7 +3687,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3695,7 +3701,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3709,7 +3715,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3723,7 +3729,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3737,7 +3743,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3751,7 +3757,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3765,7 +3771,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3779,7 +3785,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3793,7 +3799,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3807,7 +3813,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3821,7 +3827,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3835,7 +3841,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3846,10 +3852,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3863,7 +3869,7 @@
         <v>263</v>
       </c>
       <c r="D138" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3874,10 +3880,10 @@
         <v>261</v>
       </c>
       <c r="C139" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D139" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3891,7 +3897,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3905,7 +3911,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3919,7 +3925,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3930,10 +3936,10 @@
         <v>259</v>
       </c>
       <c r="C143" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D143" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3947,7 +3953,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3961,7 +3967,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3975,7 +3981,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3989,7 +3995,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4000,10 +4006,10 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4017,7 +4023,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4028,10 +4034,10 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D150" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4045,7 +4051,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4059,7 +4065,7 @@
         <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4073,7 +4079,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4084,10 +4090,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4101,7 +4107,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4115,7 +4121,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4126,10 +4132,10 @@
         <v>259</v>
       </c>
       <c r="C157" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4143,7 +4149,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4154,10 +4160,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4171,7 +4177,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4185,7 +4191,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4199,7 +4205,7 @@
         <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4213,7 +4219,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4224,10 +4230,10 @@
         <v>259</v>
       </c>
       <c r="C164" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D164" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4241,7 +4247,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4255,7 +4261,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4269,7 +4275,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4283,7 +4289,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4297,7 +4303,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4311,7 +4317,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4325,7 +4331,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4339,7 +4345,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4350,10 +4356,10 @@
         <v>259</v>
       </c>
       <c r="C173" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D173" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4367,7 +4373,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4381,7 +4387,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4392,10 +4398,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4409,7 +4415,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4423,7 +4429,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4437,7 +4443,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4451,7 +4457,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4465,7 +4471,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4479,7 +4485,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4493,7 +4499,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4507,7 +4513,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4521,7 +4527,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4535,7 +4541,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4549,7 +4555,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4563,7 +4569,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4577,7 +4583,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4591,7 +4597,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4602,10 +4608,10 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D191" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4616,10 +4622,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D192" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4630,10 +4636,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D193" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4644,10 +4650,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4658,10 +4664,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D195" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4675,7 +4681,7 @@
         <v>261</v>
       </c>
       <c r="D196" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4686,10 +4692,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4700,10 +4706,10 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D198" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4717,7 +4723,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4728,10 +4734,10 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4745,7 +4751,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4759,7 +4765,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4773,7 +4779,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4787,7 +4793,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4801,7 +4807,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4812,10 +4818,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4829,7 +4835,7 @@
         <v>261</v>
       </c>
       <c r="D207" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4843,7 +4849,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4857,7 +4863,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4871,7 +4877,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4885,7 +4891,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4899,7 +4905,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4913,7 +4919,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4927,7 +4933,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4941,7 +4947,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4955,7 +4961,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4969,7 +4975,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4983,7 +4989,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4997,7 +5003,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5011,7 +5017,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5025,7 +5031,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5039,7 +5045,7 @@
         <v>259</v>
       </c>
       <c r="D222" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5053,7 +5059,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5067,7 +5073,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5081,7 +5087,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5095,7 +5101,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5109,7 +5115,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5123,7 +5129,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5137,7 +5143,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5151,7 +5157,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5165,7 +5171,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5176,10 +5182,10 @@
         <v>259</v>
       </c>
       <c r="C232" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D232" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5193,7 +5199,7 @@
         <v>261</v>
       </c>
       <c r="D233" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5207,7 +5213,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5221,7 +5227,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5235,7 +5241,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5249,7 +5255,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5263,7 +5269,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5277,7 +5283,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5291,7 +5297,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5305,7 +5311,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5319,7 +5325,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5333,7 +5339,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5347,7 +5353,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5361,7 +5367,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5375,7 +5381,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5389,7 +5395,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5400,10 +5406,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D248" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5417,7 +5423,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5431,7 +5437,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5445,7 +5451,7 @@
         <v>260</v>
       </c>
       <c r="D251" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5459,7 +5465,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5473,7 +5479,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5487,7 +5493,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5501,7 +5507,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5512,10 +5518,10 @@
         <v>259</v>
       </c>
       <c r="C256" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
   </sheetData>
